--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>90.6079</v>
+        <v>87.02760000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>50.0027</v>
+        <v>62.98419999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>40.6053</v>
+        <v>24.0436</v>
       </c>
       <c r="G2" t="n">
-        <v>42.8639</v>
+        <v>47.6082</v>
       </c>
       <c r="H2" t="n">
-        <v>31.9931</v>
+        <v>27.3084</v>
       </c>
       <c r="I2" t="n">
-        <v>10.8707</v>
+        <v>20.3002</v>
       </c>
       <c r="J2" t="n">
-        <v>52.2721</v>
+        <v>67.6016</v>
       </c>
       <c r="K2" t="n">
-        <v>34.2363</v>
+        <v>35.0104</v>
       </c>
       <c r="L2" t="n">
-        <v>18.036</v>
+        <v>32.5916</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.407999999999999</v>
+        <v>-19.9937</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2431</v>
+        <v>-7.702</v>
       </c>
       <c r="O2" t="n">
-        <v>-7.1651</v>
+        <v>-12.2918</v>
       </c>
       <c r="P2" t="n">
-        <v>11.7204</v>
+        <v>15.6275</v>
       </c>
       <c r="Q2" t="n">
-        <v>-33.7941</v>
+        <v>-29.8874</v>
       </c>
       <c r="R2" t="n">
-        <v>45.5146</v>
+        <v>45.5151</v>
       </c>
       <c r="S2" t="n">
-        <v>29.785</v>
+        <v>16.4471</v>
       </c>
       <c r="T2" t="n">
-        <v>10.9123</v>
+        <v>6.3232</v>
       </c>
       <c r="U2" t="n">
-        <v>18.8726</v>
+        <v>10.124</v>
       </c>
       <c r="V2" t="n">
-        <v>6.239</v>
+        <v>7.344799999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>20.6129</v>
+        <v>18.9464</v>
       </c>
       <c r="X2" t="n">
-        <v>-14.3739</v>
+        <v>-11.6016</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>89.76300000000001</v>
+        <v>83.9384</v>
       </c>
       <c r="E3" t="n">
-        <v>67.7991</v>
+        <v>48.2011</v>
       </c>
       <c r="F3" t="n">
-        <v>21.9639</v>
+        <v>35.7368</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6082</v>
+        <v>42.8639</v>
       </c>
       <c r="H3" t="n">
-        <v>27.3084</v>
+        <v>31.9931</v>
       </c>
       <c r="I3" t="n">
-        <v>20.3002</v>
+        <v>10.8707</v>
       </c>
       <c r="J3" t="n">
-        <v>67.6016</v>
+        <v>52.2721</v>
       </c>
       <c r="K3" t="n">
-        <v>35.0104</v>
+        <v>34.2363</v>
       </c>
       <c r="L3" t="n">
-        <v>32.5916</v>
+        <v>18.036</v>
       </c>
       <c r="M3" t="n">
-        <v>-19.9937</v>
+        <v>-9.407999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.702</v>
+        <v>-2.2431</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.2918</v>
+        <v>-7.1651</v>
       </c>
       <c r="P3" t="n">
-        <v>15.6275</v>
+        <v>11.7204</v>
       </c>
       <c r="Q3" t="n">
-        <v>-29.8874</v>
+        <v>-33.7941</v>
       </c>
       <c r="R3" t="n">
-        <v>45.5151</v>
+        <v>45.5146</v>
       </c>
       <c r="S3" t="n">
-        <v>19.1828</v>
+        <v>23.1151</v>
       </c>
       <c r="T3" t="n">
-        <v>11.1385</v>
+        <v>9.1104</v>
       </c>
       <c r="U3" t="n">
-        <v>8.0443</v>
+        <v>14.0045</v>
       </c>
       <c r="V3" t="n">
-        <v>7.344799999999999</v>
+        <v>6.239</v>
       </c>
       <c r="W3" t="n">
-        <v>18.9464</v>
+        <v>20.6129</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.6016</v>
+        <v>-14.3739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>70.6103</v>
+        <v>73.1314</v>
       </c>
       <c r="E4" t="n">
-        <v>57.9615</v>
+        <v>47.3568</v>
       </c>
       <c r="F4" t="n">
-        <v>12.6488</v>
+        <v>25.7748</v>
       </c>
       <c r="G4" t="n">
-        <v>38.9266</v>
+        <v>58.6715</v>
       </c>
       <c r="H4" t="n">
-        <v>29.3122</v>
+        <v>22.1904</v>
       </c>
       <c r="I4" t="n">
-        <v>9.6144</v>
+        <v>36.4813</v>
       </c>
       <c r="J4" t="n">
-        <v>46.5598</v>
+        <v>75.3507</v>
       </c>
       <c r="K4" t="n">
-        <v>31.5414</v>
+        <v>24.963</v>
       </c>
       <c r="L4" t="n">
-        <v>15.0187</v>
+        <v>50.3876</v>
       </c>
       <c r="M4" t="n">
-        <v>-7.6336</v>
+        <v>-16.6791</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2293</v>
+        <v>-2.7727</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.4044</v>
+        <v>-13.9066</v>
       </c>
       <c r="P4" t="n">
-        <v>3.7112</v>
+        <v>7.813599999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-26.7617</v>
+        <v>-32.8172</v>
       </c>
       <c r="R4" t="n">
-        <v>30.4734</v>
+        <v>40.6313</v>
       </c>
       <c r="S4" t="n">
-        <v>34.1907</v>
+        <v>10.3022</v>
       </c>
       <c r="T4" t="n">
-        <v>19.9359</v>
+        <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>14.2548</v>
+        <v>8.692400000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-6.218699999999999</v>
+        <v>-3.655799999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>18.2274</v>
+        <v>3.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-24.4459</v>
+        <v>-6.8697</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>62.75</v>
+        <v>55.8819</v>
       </c>
       <c r="E5" t="n">
-        <v>44.5059</v>
+        <v>46.9183</v>
       </c>
       <c r="F5" t="n">
-        <v>18.2443</v>
+        <v>8.9635</v>
       </c>
       <c r="G5" t="n">
-        <v>21.4405</v>
+        <v>38.9266</v>
       </c>
       <c r="H5" t="n">
-        <v>22.2188</v>
+        <v>29.3122</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7779999999999996</v>
+        <v>9.6144</v>
       </c>
       <c r="J5" t="n">
-        <v>35.4669</v>
+        <v>46.5598</v>
       </c>
       <c r="K5" t="n">
-        <v>25.1737</v>
+        <v>31.5414</v>
       </c>
       <c r="L5" t="n">
-        <v>10.2932</v>
+        <v>15.0187</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.0262</v>
+        <v>-7.6336</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.9548</v>
+        <v>-2.2293</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.0715</v>
+        <v>-5.4044</v>
       </c>
       <c r="P5" t="n">
-        <v>5.4696</v>
+        <v>3.7112</v>
       </c>
       <c r="Q5" t="n">
-        <v>-29.4964</v>
+        <v>-26.7617</v>
       </c>
       <c r="R5" t="n">
-        <v>34.9664</v>
+        <v>30.4734</v>
       </c>
       <c r="S5" t="n">
-        <v>30.695</v>
+        <v>19.4628</v>
       </c>
       <c r="T5" t="n">
-        <v>23.7385</v>
+        <v>8.892900000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>6.9564</v>
+        <v>10.5698</v>
       </c>
       <c r="V5" t="n">
-        <v>5.1448</v>
+        <v>-6.218699999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>14.7968</v>
+        <v>18.2274</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.6518</v>
+        <v>-24.4459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>56.102</v>
+        <v>50.6402</v>
       </c>
       <c r="E6" t="n">
-        <v>33.8501</v>
+        <v>31.3994</v>
       </c>
       <c r="F6" t="n">
-        <v>22.252</v>
+        <v>19.2412</v>
       </c>
       <c r="G6" t="n">
-        <v>58.6715</v>
+        <v>21.4405</v>
       </c>
       <c r="H6" t="n">
-        <v>22.1904</v>
+        <v>22.2188</v>
       </c>
       <c r="I6" t="n">
-        <v>36.4813</v>
+        <v>-0.7779999999999996</v>
       </c>
       <c r="J6" t="n">
-        <v>75.3507</v>
+        <v>35.4669</v>
       </c>
       <c r="K6" t="n">
-        <v>24.963</v>
+        <v>25.1737</v>
       </c>
       <c r="L6" t="n">
-        <v>50.3876</v>
+        <v>10.2932</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.6791</v>
+        <v>-14.0262</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.7727</v>
+        <v>-2.9548</v>
       </c>
       <c r="O6" t="n">
-        <v>-13.9066</v>
+        <v>-11.0715</v>
       </c>
       <c r="P6" t="n">
-        <v>7.813599999999999</v>
+        <v>5.4696</v>
       </c>
       <c r="Q6" t="n">
-        <v>-32.8172</v>
+        <v>-29.4964</v>
       </c>
       <c r="R6" t="n">
-        <v>40.6313</v>
+        <v>34.9664</v>
       </c>
       <c r="S6" t="n">
-        <v>-6.7273</v>
+        <v>18.585</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.897</v>
+        <v>10.632</v>
       </c>
       <c r="U6" t="n">
-        <v>5.1699</v>
+        <v>7.9531</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.655799999999999</v>
+        <v>5.1448</v>
       </c>
       <c r="W6" t="n">
-        <v>3.214</v>
+        <v>14.7968</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.8697</v>
+        <v>-9.6518</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>55.138</v>
+        <v>49.2187</v>
       </c>
       <c r="E7" t="n">
-        <v>38.998</v>
+        <v>34.1023</v>
       </c>
       <c r="F7" t="n">
-        <v>16.1405</v>
+        <v>15.1162</v>
       </c>
       <c r="G7" t="n">
         <v>28.2159</v>
@@ -1000,13 +1000,13 @@
         <v>32.2316</v>
       </c>
       <c r="S7" t="n">
-        <v>21.5446</v>
+        <v>15.6249</v>
       </c>
       <c r="T7" t="n">
-        <v>12.0125</v>
+        <v>7.1169</v>
       </c>
       <c r="U7" t="n">
-        <v>9.532299999999999</v>
+        <v>8.5082</v>
       </c>
       <c r="V7" t="n">
         <v>6.3547</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>41.3123</v>
+        <v>48.6675</v>
       </c>
       <c r="E8" t="n">
-        <v>31.3838</v>
+        <v>25.5574</v>
       </c>
       <c r="F8" t="n">
-        <v>9.9285</v>
+        <v>23.1103</v>
       </c>
       <c r="G8" t="n">
-        <v>35.9398</v>
+        <v>25.0543</v>
       </c>
       <c r="H8" t="n">
-        <v>29.5247</v>
+        <v>1.479000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>6.415</v>
+        <v>23.5749</v>
       </c>
       <c r="J8" t="n">
-        <v>50.0881</v>
+        <v>36.6141</v>
       </c>
       <c r="K8" t="n">
-        <v>37.9954</v>
+        <v>9.654199999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>12.0922</v>
+        <v>26.9601</v>
       </c>
       <c r="M8" t="n">
-        <v>-14.1484</v>
+        <v>-11.5603</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.4711</v>
+        <v>-8.1753</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.677700000000001</v>
+        <v>-3.3852</v>
       </c>
       <c r="P8" t="n">
-        <v>1.758</v>
+        <v>7.8138</v>
       </c>
       <c r="Q8" t="n">
-        <v>-36.5289</v>
+        <v>-27.5431</v>
       </c>
       <c r="R8" t="n">
-        <v>38.2874</v>
+        <v>35.3571</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4154</v>
+        <v>7.3492</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5700000000000001</v>
+        <v>2.3047</v>
       </c>
       <c r="U8" t="n">
-        <v>2.9855</v>
+        <v>5.0447</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1991</v>
+        <v>8.4504</v>
       </c>
       <c r="W8" t="n">
-        <v>18.3949</v>
+        <v>14.1815</v>
       </c>
       <c r="X8" t="n">
-        <v>-17.1958</v>
+        <v>-5.7311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>32.7126</v>
+        <v>48.0722</v>
       </c>
       <c r="E9" t="n">
-        <v>14.2744</v>
+        <v>35.5686</v>
       </c>
       <c r="F9" t="n">
-        <v>18.4385</v>
+        <v>12.5038</v>
       </c>
       <c r="G9" t="n">
-        <v>25.0543</v>
+        <v>35.9398</v>
       </c>
       <c r="H9" t="n">
-        <v>1.479000000000001</v>
+        <v>29.5247</v>
       </c>
       <c r="I9" t="n">
-        <v>23.5749</v>
+        <v>6.415</v>
       </c>
       <c r="J9" t="n">
-        <v>36.6141</v>
+        <v>50.0881</v>
       </c>
       <c r="K9" t="n">
-        <v>9.654199999999999</v>
+        <v>37.9954</v>
       </c>
       <c r="L9" t="n">
-        <v>26.9601</v>
+        <v>12.0922</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.5603</v>
+        <v>-14.1484</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.1753</v>
+        <v>-8.4711</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.3852</v>
+        <v>-5.677700000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8138</v>
+        <v>1.758</v>
       </c>
       <c r="Q9" t="n">
-        <v>-27.5431</v>
+        <v>-36.5289</v>
       </c>
       <c r="R9" t="n">
-        <v>35.3571</v>
+        <v>38.2874</v>
       </c>
       <c r="S9" t="n">
-        <v>-8.605699999999999</v>
+        <v>9.1755</v>
       </c>
       <c r="T9" t="n">
-        <v>-8.978299999999999</v>
+        <v>3.6147</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3726999999999999</v>
+        <v>5.5609</v>
       </c>
       <c r="V9" t="n">
-        <v>8.4504</v>
+        <v>1.1991</v>
       </c>
       <c r="W9" t="n">
-        <v>14.1815</v>
+        <v>18.3949</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.7311</v>
+        <v>-17.1958</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>26.8108</v>
+        <v>42.2043</v>
       </c>
       <c r="E10" t="n">
-        <v>17.9724</v>
+        <v>22.2216</v>
       </c>
       <c r="F10" t="n">
-        <v>8.8386</v>
+        <v>19.9826</v>
       </c>
       <c r="G10" t="n">
-        <v>16.5567</v>
+        <v>18.0578</v>
       </c>
       <c r="H10" t="n">
-        <v>16.6833</v>
+        <v>0.3029999999999995</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1267</v>
+        <v>17.7549</v>
       </c>
       <c r="J10" t="n">
-        <v>20.5925</v>
+        <v>32.8849</v>
       </c>
       <c r="K10" t="n">
-        <v>18.2858</v>
+        <v>8.3727</v>
       </c>
       <c r="L10" t="n">
-        <v>2.3067</v>
+        <v>24.5126</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0358</v>
+        <v>-14.8268</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6025</v>
+        <v>-8.069099999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4333</v>
+        <v>-6.757499999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9303</v>
+        <v>5.2745</v>
       </c>
       <c r="Q10" t="n">
-        <v>-12.3065</v>
+        <v>-33.208</v>
       </c>
       <c r="R10" t="n">
-        <v>15.2368</v>
+        <v>38.4826</v>
       </c>
       <c r="S10" t="n">
-        <v>11.6533</v>
+        <v>8.2394</v>
       </c>
       <c r="T10" t="n">
-        <v>6.4145</v>
+        <v>1.9929</v>
       </c>
       <c r="U10" t="n">
-        <v>5.2387</v>
+        <v>6.2467</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.3294</v>
+        <v>10.6326</v>
       </c>
       <c r="W10" t="n">
-        <v>3.2717</v>
+        <v>20.5517</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.6011</v>
+        <v>-9.9192</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>26.5846</v>
+        <v>31.5724</v>
       </c>
       <c r="E11" t="n">
-        <v>10.8381</v>
+        <v>14.3998</v>
       </c>
       <c r="F11" t="n">
-        <v>15.7461</v>
+        <v>17.1724</v>
       </c>
       <c r="G11" t="n">
-        <v>18.0578</v>
+        <v>14.4435</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3029999999999995</v>
+        <v>4.5818</v>
       </c>
       <c r="I11" t="n">
-        <v>17.7549</v>
+        <v>9.8619</v>
       </c>
       <c r="J11" t="n">
-        <v>32.8849</v>
+        <v>20.4483</v>
       </c>
       <c r="K11" t="n">
-        <v>8.3727</v>
+        <v>6.396800000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>24.5126</v>
+        <v>14.0513</v>
       </c>
       <c r="M11" t="n">
-        <v>-14.8268</v>
+        <v>-6.0048</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.069099999999999</v>
+        <v>-1.8149</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.757499999999999</v>
+        <v>-4.1897</v>
       </c>
       <c r="P11" t="n">
-        <v>5.2745</v>
+        <v>15.432</v>
       </c>
       <c r="Q11" t="n">
-        <v>-33.208</v>
+        <v>-7.8135</v>
       </c>
       <c r="R11" t="n">
-        <v>38.4826</v>
+        <v>23.2457</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.3803</v>
+        <v>3.2691</v>
       </c>
       <c r="T11" t="n">
-        <v>-9.3903</v>
+        <v>-0.1751000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>2.0103</v>
+        <v>3.4445</v>
       </c>
       <c r="V11" t="n">
-        <v>10.6326</v>
+        <v>-1.5726</v>
       </c>
       <c r="W11" t="n">
-        <v>20.5517</v>
+        <v>1.9405</v>
       </c>
       <c r="X11" t="n">
-        <v>-9.9192</v>
+        <v>-3.5131</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>24.877</v>
+        <v>22.3796</v>
       </c>
       <c r="E12" t="n">
-        <v>11.2666</v>
+        <v>14.8771</v>
       </c>
       <c r="F12" t="n">
-        <v>13.61</v>
+        <v>7.502700000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>14.4435</v>
+        <v>16.5567</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5818</v>
+        <v>16.6833</v>
       </c>
       <c r="I12" t="n">
-        <v>9.8619</v>
+        <v>-0.1267</v>
       </c>
       <c r="J12" t="n">
-        <v>20.4483</v>
+        <v>20.5925</v>
       </c>
       <c r="K12" t="n">
-        <v>6.396800000000001</v>
+        <v>18.2858</v>
       </c>
       <c r="L12" t="n">
-        <v>14.0513</v>
+        <v>2.3067</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.0048</v>
+        <v>-4.0358</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8149</v>
+        <v>-1.6025</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.1897</v>
+        <v>-2.4333</v>
       </c>
       <c r="P12" t="n">
-        <v>15.432</v>
+        <v>2.9303</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.8135</v>
+        <v>-12.3065</v>
       </c>
       <c r="R12" t="n">
-        <v>23.2457</v>
+        <v>15.2368</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.4261</v>
+        <v>7.2221</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3084</v>
+        <v>3.3191</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.118</v>
+        <v>3.9029</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5726</v>
+        <v>-4.3294</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9405</v>
+        <v>3.2717</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5131</v>
+        <v>-7.6011</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>7.391799999999999</v>
+        <v>12.4398</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6236</v>
+        <v>4.765499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>4.7681</v>
+        <v>7.6744</v>
       </c>
       <c r="G13" t="n">
         <v>-6.1354</v>
@@ -1468,13 +1468,13 @@
         <v>23.2457</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7739</v>
+        <v>5.8219</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4417999999999998</v>
+        <v>2.5839</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3321999999999999</v>
+        <v>3.2379</v>
       </c>
       <c r="V13" t="n">
         <v>2.205</v>
@@ -1501,13 +1501,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8717999999999999</v>
+        <v>0.06770000000000009</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.1236</v>
+        <v>-1.4562</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2516</v>
+        <v>1.524</v>
       </c>
       <c r="G14" t="n">
         <v>-2.2492</v>
@@ -1546,13 +1546,13 @@
         <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01390000000000002</v>
+        <v>0.9533999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2338</v>
+        <v>0.4334999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2475</v>
+        <v>0.5198</v>
       </c>
       <c r="V14" t="n">
         <v>0.387</v>
@@ -1579,13 +1579,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.0692</v>
+        <v>-7.5908</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.23</v>
+        <v>-4.9967</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8391</v>
+        <v>-2.594</v>
       </c>
       <c r="G15" t="n">
         <v>-10.0939</v>
@@ -1624,13 +1624,13 @@
         <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9947</v>
+        <v>0.4835</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6532</v>
+        <v>-0.42</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6583999999999999</v>
+        <v>0.9036</v>
       </c>
       <c r="V15" t="n">
         <v>2.2149</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>574.7193</v>
+        <v>597.6509</v>
       </c>
       <c r="E16" t="n">
-        <v>373.1225999999999</v>
+        <v>381.8992</v>
       </c>
       <c r="F16" t="n">
-        <v>201.5971</v>
+        <v>215.7523</v>
       </c>
       <c r="G16" t="n">
         <v>329.3002</v>
@@ -1687,28 +1687,28 @@
         <v>-151.141</v>
       </c>
       <c r="N16" t="n">
-        <v>-56.5818</v>
+        <v>-56.58179999999999</v>
       </c>
       <c r="O16" t="n">
         <v>-94.56029999999998</v>
       </c>
       <c r="P16" t="n">
-        <v>87.9041</v>
+        <v>87.90409999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-319.3827999999999</v>
+        <v>-319.3828</v>
       </c>
       <c r="R16" t="n">
         <v>407.2899</v>
       </c>
       <c r="S16" t="n">
-        <v>123.1205</v>
+        <v>146.0512</v>
       </c>
       <c r="T16" t="n">
-        <v>48.56300000000001</v>
+        <v>57.33909999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>74.55760000000001</v>
+        <v>88.71300000000001</v>
       </c>
       <c r="V16" t="n">
         <v>34.3958</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>73.1314</v>
+        <v>55.8819</v>
       </c>
       <c r="E4" t="n">
-        <v>47.3568</v>
+        <v>46.9183</v>
       </c>
       <c r="F4" t="n">
-        <v>25.7748</v>
+        <v>8.9635</v>
       </c>
       <c r="G4" t="n">
-        <v>58.6715</v>
+        <v>38.9266</v>
       </c>
       <c r="H4" t="n">
-        <v>22.1904</v>
+        <v>29.3122</v>
       </c>
       <c r="I4" t="n">
-        <v>36.4813</v>
+        <v>9.6144</v>
       </c>
       <c r="J4" t="n">
-        <v>75.3507</v>
+        <v>46.5598</v>
       </c>
       <c r="K4" t="n">
-        <v>24.963</v>
+        <v>31.5414</v>
       </c>
       <c r="L4" t="n">
-        <v>50.3876</v>
+        <v>15.0187</v>
       </c>
       <c r="M4" t="n">
-        <v>-16.6791</v>
+        <v>-7.6336</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.7727</v>
+        <v>-2.2293</v>
       </c>
       <c r="O4" t="n">
-        <v>-13.9066</v>
+        <v>-5.4044</v>
       </c>
       <c r="P4" t="n">
-        <v>7.813599999999999</v>
+        <v>3.7112</v>
       </c>
       <c r="Q4" t="n">
-        <v>-32.8172</v>
+        <v>-26.7617</v>
       </c>
       <c r="R4" t="n">
-        <v>40.6313</v>
+        <v>30.4734</v>
       </c>
       <c r="S4" t="n">
-        <v>10.3022</v>
+        <v>19.4628</v>
       </c>
       <c r="T4" t="n">
-        <v>1.61</v>
+        <v>8.892900000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>8.692400000000001</v>
+        <v>10.5698</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.655799999999999</v>
+        <v>-6.218699999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>3.214</v>
+        <v>18.2274</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.8697</v>
+        <v>-24.4459</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>55.8819</v>
+        <v>50.6402</v>
       </c>
       <c r="E5" t="n">
-        <v>46.9183</v>
+        <v>31.3994</v>
       </c>
       <c r="F5" t="n">
-        <v>8.9635</v>
+        <v>19.2412</v>
       </c>
       <c r="G5" t="n">
-        <v>38.9266</v>
+        <v>21.4405</v>
       </c>
       <c r="H5" t="n">
-        <v>29.3122</v>
+        <v>22.2188</v>
       </c>
       <c r="I5" t="n">
-        <v>9.6144</v>
+        <v>-0.7779999999999996</v>
       </c>
       <c r="J5" t="n">
-        <v>46.5598</v>
+        <v>35.4669</v>
       </c>
       <c r="K5" t="n">
-        <v>31.5414</v>
+        <v>25.1737</v>
       </c>
       <c r="L5" t="n">
-        <v>15.0187</v>
+        <v>10.2932</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.6336</v>
+        <v>-14.0262</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.2293</v>
+        <v>-2.9548</v>
       </c>
       <c r="O5" t="n">
-        <v>-5.4044</v>
+        <v>-11.0715</v>
       </c>
       <c r="P5" t="n">
-        <v>3.7112</v>
+        <v>5.4696</v>
       </c>
       <c r="Q5" t="n">
-        <v>-26.7617</v>
+        <v>-29.4964</v>
       </c>
       <c r="R5" t="n">
-        <v>30.4734</v>
+        <v>34.9664</v>
       </c>
       <c r="S5" t="n">
-        <v>19.4628</v>
+        <v>18.585</v>
       </c>
       <c r="T5" t="n">
-        <v>8.892900000000001</v>
+        <v>10.632</v>
       </c>
       <c r="U5" t="n">
-        <v>10.5698</v>
+        <v>7.9531</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.218699999999999</v>
+        <v>5.1448</v>
       </c>
       <c r="W5" t="n">
-        <v>18.2274</v>
+        <v>14.7968</v>
       </c>
       <c r="X5" t="n">
-        <v>-24.4459</v>
+        <v>-9.6518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>50.6402</v>
+        <v>49.2187</v>
       </c>
       <c r="E6" t="n">
-        <v>31.3994</v>
+        <v>34.1023</v>
       </c>
       <c r="F6" t="n">
-        <v>19.2412</v>
+        <v>15.1162</v>
       </c>
       <c r="G6" t="n">
-        <v>21.4405</v>
+        <v>28.2159</v>
       </c>
       <c r="H6" t="n">
-        <v>22.2188</v>
+        <v>26.2232</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7779999999999996</v>
+        <v>1.9922</v>
       </c>
       <c r="J6" t="n">
-        <v>35.4669</v>
+        <v>41.3569</v>
       </c>
       <c r="K6" t="n">
-        <v>25.1737</v>
+        <v>31.7983</v>
       </c>
       <c r="L6" t="n">
-        <v>10.2932</v>
+        <v>9.5587</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.0262</v>
+        <v>-13.1411</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.9548</v>
+        <v>-5.5747</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.0715</v>
+        <v>-7.5664</v>
       </c>
       <c r="P6" t="n">
-        <v>5.4696</v>
+        <v>-0.9765999999999997</v>
       </c>
       <c r="Q6" t="n">
-        <v>-29.4964</v>
+        <v>-33.2081</v>
       </c>
       <c r="R6" t="n">
-        <v>34.9664</v>
+        <v>32.2316</v>
       </c>
       <c r="S6" t="n">
-        <v>18.585</v>
+        <v>15.6249</v>
       </c>
       <c r="T6" t="n">
-        <v>10.632</v>
+        <v>7.1169</v>
       </c>
       <c r="U6" t="n">
-        <v>7.9531</v>
+        <v>8.5082</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1448</v>
+        <v>6.3547</v>
       </c>
       <c r="W6" t="n">
-        <v>14.7968</v>
+        <v>18.8368</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.6518</v>
+        <v>-12.4823</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>49.2187</v>
+        <v>48.6675</v>
       </c>
       <c r="E7" t="n">
-        <v>34.1023</v>
+        <v>25.5574</v>
       </c>
       <c r="F7" t="n">
-        <v>15.1162</v>
+        <v>23.1103</v>
       </c>
       <c r="G7" t="n">
-        <v>28.2159</v>
+        <v>25.0543</v>
       </c>
       <c r="H7" t="n">
-        <v>26.2232</v>
+        <v>1.479000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9922</v>
+        <v>23.5749</v>
       </c>
       <c r="J7" t="n">
-        <v>41.3569</v>
+        <v>36.6141</v>
       </c>
       <c r="K7" t="n">
-        <v>31.7983</v>
+        <v>9.654199999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5587</v>
+        <v>26.9601</v>
       </c>
       <c r="M7" t="n">
-        <v>-13.1411</v>
+        <v>-11.5603</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.5747</v>
+        <v>-8.1753</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.5664</v>
+        <v>-3.3852</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9765999999999997</v>
+        <v>7.8138</v>
       </c>
       <c r="Q7" t="n">
-        <v>-33.2081</v>
+        <v>-27.5431</v>
       </c>
       <c r="R7" t="n">
-        <v>32.2316</v>
+        <v>35.3571</v>
       </c>
       <c r="S7" t="n">
-        <v>15.6249</v>
+        <v>7.3492</v>
       </c>
       <c r="T7" t="n">
-        <v>7.1169</v>
+        <v>2.3047</v>
       </c>
       <c r="U7" t="n">
-        <v>8.5082</v>
+        <v>5.0447</v>
       </c>
       <c r="V7" t="n">
-        <v>6.3547</v>
+        <v>8.4504</v>
       </c>
       <c r="W7" t="n">
-        <v>18.8368</v>
+        <v>14.1815</v>
       </c>
       <c r="X7" t="n">
-        <v>-12.4823</v>
+        <v>-5.7311</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>48.6675</v>
+        <v>48.0722</v>
       </c>
       <c r="E8" t="n">
-        <v>25.5574</v>
+        <v>35.5686</v>
       </c>
       <c r="F8" t="n">
-        <v>23.1103</v>
+        <v>12.5038</v>
       </c>
       <c r="G8" t="n">
-        <v>25.0543</v>
+        <v>35.9398</v>
       </c>
       <c r="H8" t="n">
-        <v>1.479000000000001</v>
+        <v>29.5247</v>
       </c>
       <c r="I8" t="n">
-        <v>23.5749</v>
+        <v>6.415</v>
       </c>
       <c r="J8" t="n">
-        <v>36.6141</v>
+        <v>50.0881</v>
       </c>
       <c r="K8" t="n">
-        <v>9.654199999999999</v>
+        <v>37.9954</v>
       </c>
       <c r="L8" t="n">
-        <v>26.9601</v>
+        <v>12.0922</v>
       </c>
       <c r="M8" t="n">
-        <v>-11.5603</v>
+        <v>-14.1484</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.1753</v>
+        <v>-8.4711</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.3852</v>
+        <v>-5.677700000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8138</v>
+        <v>1.758</v>
       </c>
       <c r="Q8" t="n">
-        <v>-27.5431</v>
+        <v>-36.5289</v>
       </c>
       <c r="R8" t="n">
-        <v>35.3571</v>
+        <v>38.2874</v>
       </c>
       <c r="S8" t="n">
-        <v>7.3492</v>
+        <v>9.1755</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3047</v>
+        <v>3.6147</v>
       </c>
       <c r="U8" t="n">
-        <v>5.0447</v>
+        <v>5.5609</v>
       </c>
       <c r="V8" t="n">
-        <v>8.4504</v>
+        <v>1.1991</v>
       </c>
       <c r="W8" t="n">
-        <v>14.1815</v>
+        <v>18.3949</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.7311</v>
+        <v>-17.1958</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>48.0722</v>
+        <v>46.9404</v>
       </c>
       <c r="E9" t="n">
-        <v>35.5686</v>
+        <v>46.9404</v>
       </c>
       <c r="F9" t="n">
-        <v>12.5038</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>35.9398</v>
+        <v>46.9404</v>
       </c>
       <c r="H9" t="n">
-        <v>29.5247</v>
+        <v>17.8055</v>
       </c>
       <c r="I9" t="n">
-        <v>6.415</v>
+        <v>29.1356</v>
       </c>
       <c r="J9" t="n">
-        <v>50.0881</v>
+        <v>46.9404</v>
       </c>
       <c r="K9" t="n">
-        <v>37.9954</v>
+        <v>17.8055</v>
       </c>
       <c r="L9" t="n">
-        <v>12.0922</v>
+        <v>29.1356</v>
       </c>
       <c r="M9" t="n">
-        <v>-14.1484</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.4711</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.677700000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.758</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-36.5289</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>38.2874</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>9.1755</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6147</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>5.5609</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1991</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>18.3949</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-17.1958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>22.3796</v>
+        <v>26.1913</v>
       </c>
       <c r="E12" t="n">
-        <v>14.8771</v>
+        <v>0.4164000000000005</v>
       </c>
       <c r="F12" t="n">
-        <v>7.502700000000001</v>
+        <v>25.7748</v>
       </c>
       <c r="G12" t="n">
-        <v>16.5567</v>
+        <v>11.731</v>
       </c>
       <c r="H12" t="n">
-        <v>16.6833</v>
+        <v>4.3853</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1267</v>
+        <v>7.3459</v>
       </c>
       <c r="J12" t="n">
-        <v>20.5925</v>
+        <v>28.4101</v>
       </c>
       <c r="K12" t="n">
-        <v>18.2858</v>
+        <v>7.1577</v>
       </c>
       <c r="L12" t="n">
-        <v>2.3067</v>
+        <v>21.2525</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0358</v>
+        <v>-16.6791</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6025</v>
+        <v>-2.7727</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.4333</v>
+        <v>-13.9066</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9303</v>
+        <v>7.813599999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.3065</v>
+        <v>-32.8172</v>
       </c>
       <c r="R12" t="n">
-        <v>15.2368</v>
+        <v>40.6313</v>
       </c>
       <c r="S12" t="n">
-        <v>7.2221</v>
+        <v>10.3022</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3191</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>3.9029</v>
+        <v>8.692400000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.3294</v>
+        <v>-3.655799999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2717</v>
+        <v>3.214</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.6011</v>
+        <v>-6.8697</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>12.4398</v>
+        <v>20.5448</v>
       </c>
       <c r="E13" t="n">
-        <v>4.765499999999999</v>
+        <v>13.0422</v>
       </c>
       <c r="F13" t="n">
-        <v>7.6744</v>
+        <v>7.502700000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.1354</v>
+        <v>14.7217</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001100000000000323</v>
+        <v>15.4554</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.1365</v>
+        <v>-0.7337</v>
       </c>
       <c r="J13" t="n">
-        <v>7.673900000000001</v>
+        <v>18.7575</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8218</v>
+        <v>17.0579</v>
       </c>
       <c r="L13" t="n">
-        <v>3.851900000000001</v>
+        <v>1.6997</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.8095</v>
+        <v>-4.0358</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.8209</v>
+        <v>-1.6025</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.9887</v>
+        <v>-2.4333</v>
       </c>
       <c r="P13" t="n">
-        <v>10.5484</v>
+        <v>2.9303</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6971</v>
+        <v>-12.3065</v>
       </c>
       <c r="R13" t="n">
-        <v>23.2457</v>
+        <v>15.2368</v>
       </c>
       <c r="S13" t="n">
-        <v>5.8219</v>
+        <v>7.2221</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5839</v>
+        <v>3.3191</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2379</v>
+        <v>3.9029</v>
       </c>
       <c r="V13" t="n">
-        <v>2.205</v>
+        <v>-4.3294</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2048</v>
+        <v>3.2717</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.9998</v>
+        <v>-7.6011</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. BAYO GARCIA</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06770000000000009</v>
+        <v>12.4398</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4562</v>
+        <v>4.765499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.524</v>
+        <v>7.6744</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2492</v>
+        <v>-6.1354</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2291</v>
+        <v>0.001100000000000323</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.4783</v>
+        <v>-6.1365</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.8898</v>
+        <v>7.673900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7790000000000001</v>
+        <v>3.8218</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.6688</v>
+        <v>3.851900000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3594999999999999</v>
+        <v>-13.8095</v>
       </c>
       <c r="N14" t="n">
-        <v>0.45</v>
+        <v>-3.8209</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8095</v>
+        <v>-9.9887</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>10.5484</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-12.6971</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9767</v>
+        <v>23.2457</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9533999999999999</v>
+        <v>5.8219</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4334999999999999</v>
+        <v>2.5839</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5198</v>
+        <v>3.2379</v>
       </c>
       <c r="V14" t="n">
-        <v>0.387</v>
+        <v>2.205</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>7.2048</v>
       </c>
       <c r="X14" t="n">
-        <v>0.387</v>
+        <v>-4.9998</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,147 +1576,381 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.5908</v>
+        <v>1.835</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.9967</v>
+        <v>1.835</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.594</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.0939</v>
+        <v>1.835</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1269</v>
+        <v>1.228</v>
       </c>
       <c r="I15" t="n">
-        <v>-8.9671</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.5798</v>
+        <v>1.835</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4745</v>
+        <v>1.228</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.0544</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.5142</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6014</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.9129</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.3208</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1255</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4835</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9036</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2149</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3238</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>I. MACÍAS MERINO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G. BAYO GARCIA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.06770000000000009</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.4562</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-2.2492</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.2291</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3.4783</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1.8898</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7790000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-2.6688</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.3594999999999999</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.8095</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.9533999999999999</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.4334999999999999</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5198</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.387</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I. MACIAS MERINO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-7.8978</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-5.3037</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-2.594</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-10.4008</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.4339</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-8.9671</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-4.8868</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.1676000000000001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-5.0544</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-5.5142</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1.6014</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-3.9129</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.1255</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.9036</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.2149</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.3238</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.1088</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>TQ-CB PRAT</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C19" t="n">
         <v>26</v>
       </c>
-      <c r="D16" t="n">
-        <v>597.6509</v>
-      </c>
-      <c r="E16" t="n">
-        <v>381.8992</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="D19" t="n">
+        <v>597.6514000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>381.8993</v>
+      </c>
+      <c r="F19" t="n">
         <v>215.7523</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G19" t="n">
         <v>329.3002</v>
       </c>
-      <c r="H16" t="n">
-        <v>211.9212</v>
-      </c>
-      <c r="I16" t="n">
-        <v>117.3789</v>
-      </c>
-      <c r="J16" t="n">
-        <v>480.4402000000001</v>
-      </c>
-      <c r="K16" t="n">
-        <v>268.5033</v>
-      </c>
-      <c r="L16" t="n">
-        <v>211.9374</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="H19" t="n">
+        <v>211.9217</v>
+      </c>
+      <c r="I19" t="n">
+        <v>117.3791</v>
+      </c>
+      <c r="J19" t="n">
+        <v>480.4400000000001</v>
+      </c>
+      <c r="K19" t="n">
+        <v>268.5037</v>
+      </c>
+      <c r="L19" t="n">
+        <v>211.9379</v>
+      </c>
+      <c r="M19" t="n">
         <v>-151.141</v>
       </c>
-      <c r="N16" t="n">
-        <v>-56.58179999999999</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-94.56029999999998</v>
-      </c>
-      <c r="P16" t="n">
-        <v>87.90409999999999</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N19" t="n">
+        <v>-56.5818</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-94.5603</v>
+      </c>
+      <c r="P19" t="n">
+        <v>87.9041</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-319.3828</v>
       </c>
-      <c r="R16" t="n">
-        <v>407.2899</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R19" t="n">
+        <v>407.2898999999999</v>
+      </c>
+      <c r="S19" t="n">
         <v>146.0512</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T19" t="n">
         <v>57.33909999999999</v>
       </c>
-      <c r="U16" t="n">
-        <v>88.71300000000001</v>
-      </c>
-      <c r="V16" t="n">
-        <v>34.3958</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="U19" t="n">
+        <v>88.71299999999999</v>
+      </c>
+      <c r="V19" t="n">
+        <v>34.39580000000001</v>
+      </c>
+      <c r="W19" t="n">
         <v>163.5032</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X19" t="n">
         <v>-129.1071</v>
       </c>
     </row>
